--- a/PDF/test_questions_en.xlsx
+++ b/PDF/test_questions_en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscik35\Desktop\PROJECTS\Project_Hydroscand-Hoses\PDF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767736E3-AD81-4B42-89ED-751820543F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8E20F-7B2D-4491-8599-9993848D556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -962,7 +962,7 @@
   <cols>
     <col min="1" max="1" width="72" style="15" customWidth="1"/>
     <col min="2" max="2" width="162.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="111.28515625" customWidth="1"/>
     <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -976,19 +976,19 @@
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>113</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>134</v>
       </c>
@@ -5377,6 +5377,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="de79c845-8446-4be5-984e-d25d943047ee" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe93da8c-6526-4e42-9742-6d42572bf3ee">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x0101009BB79CDB3FA68A418433DE5208DB5B1C" ma:contentTypeVersion="15" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="12703850505ea0866cc40662c7c74748">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe93da8c-6526-4e42-9742-6d42572bf3ee" xmlns:ns3="de79c845-8446-4be5-984e-d25d943047ee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="09c792e958a7c8617cec18408b828c0c" ns2:_="" ns3:_="">
     <xsd:import namespace="fe93da8c-6526-4e42-9742-6d42572bf3ee"/>
@@ -5611,17 +5622,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="de79c845-8446-4be5-984e-d25d943047ee" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe93da8c-6526-4e42-9742-6d42572bf3ee">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F7CE8D-C2DA-435A-A053-07DF1AE8F5DC}">
   <ds:schemaRefs>
@@ -5631,6 +5631,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFACDE9-9D27-4F7F-9EF2-8EADEA1B5F32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="de79c845-8446-4be5-984e-d25d943047ee"/>
+    <ds:schemaRef ds:uri="fe93da8c-6526-4e42-9742-6d42572bf3ee"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C27AD6-059D-4BD4-A030-340565F19CB5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5647,15 +5658,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFACDE9-9D27-4F7F-9EF2-8EADEA1B5F32}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="de79c845-8446-4be5-984e-d25d943047ee"/>
-    <ds:schemaRef ds:uri="fe93da8c-6526-4e42-9742-6d42572bf3ee"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/PDF/test_questions_en.xlsx
+++ b/PDF/test_questions_en.xlsx
@@ -579,7 +579,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +597,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -620,7 +626,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -702,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -713,44 +719,41 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -1061,8 +1064,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="15" width="72.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="162.29071428571427" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="111.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="162.29071428571427" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="111.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -1077,21 +1080,21 @@
       <c r="B2" s="6"/>
       <c r="C2" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="34.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="33.75" customFormat="1" s="1">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="34.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="33.75" customFormat="1" s="1">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="34.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="33.75" customFormat="1" s="1">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1108,7 +1111,7 @@
       <c r="B7" s="6"/>
       <c r="C7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="97.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A8" s="7" t="s">
         <v>4</v>
       </c>

--- a/PDF/test_questions_en.xlsx
+++ b/PDF/test_questions_en.xlsx
@@ -579,7 +579,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,7 +601,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -622,12 +622,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -708,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -743,11 +737,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -756,7 +747,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1063,9 +1054,9 @@
   <dimension ref="A1:C999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="15" width="72.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="162.29071428571427" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="111.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="14" width="72.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="162.29071428571427" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="111.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -1122,7 +1113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="58.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
@@ -1131,7 +1122,7 @@
       </c>
       <c r="C9" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="58.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
@@ -1151,7 +1142,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="58.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A12" s="7" t="s">
         <v>14</v>
       </c>
@@ -1160,7 +1151,7 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="32.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1160,7 @@
       </c>
       <c r="C13" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="58.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
@@ -1178,7 +1169,7 @@
       </c>
       <c r="C14" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1187,7 +1178,7 @@
       </c>
       <c r="C15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="97.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
@@ -1196,7 +1187,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
@@ -1205,7 +1196,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A18" s="7" t="s">
         <v>26</v>
       </c>
@@ -1214,7 +1205,7 @@
       </c>
       <c r="C18" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A19" s="7" t="s">
         <v>28</v>
       </c>
@@ -1223,7 +1214,7 @@
       </c>
       <c r="C19" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="45">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="44.25">
       <c r="A20" s="7" t="s">
         <v>30</v>
       </c>
@@ -1232,7 +1223,7 @@
       </c>
       <c r="C20" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A21" s="7" t="s">
         <v>32</v>
       </c>
@@ -1241,7 +1232,7 @@
       </c>
       <c r="C21" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="58.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A22" s="7" t="s">
         <v>34</v>
       </c>
@@ -1252,7 +1243,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A23" s="7" t="s">
         <v>37</v>
       </c>
@@ -1263,7 +1254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="97.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A24" s="8" t="s">
         <v>40</v>
       </c>
@@ -1272,7 +1263,7 @@
       </c>
       <c r="C24" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="84.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="82.5" customFormat="1" s="1">
       <c r="A25" s="8" t="s">
         <v>42</v>
       </c>
@@ -1281,7 +1272,7 @@
       </c>
       <c r="C25" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A26" s="8" t="s">
         <v>44</v>
       </c>
@@ -1290,7 +1281,7 @@
       </c>
       <c r="C26" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="45" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A27" s="8" t="s">
         <v>46</v>
       </c>
@@ -1299,7 +1290,7 @@
       </c>
       <c r="C27" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="32.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A28" s="8" t="s">
         <v>48</v>
       </c>
@@ -1308,18 +1299,18 @@
       </c>
       <c r="C28" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A29" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A30" s="8" t="s">
         <v>53</v>
       </c>
@@ -1330,7 +1321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A31" s="8" t="s">
         <v>56</v>
       </c>
@@ -1341,16 +1332,16 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A32" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>60</v>
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A33" s="8" t="s">
         <v>61</v>
       </c>
@@ -1359,7 +1350,7 @@
       </c>
       <c r="C33" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A34" s="8" t="s">
         <v>63</v>
       </c>
@@ -1370,7 +1361,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A35" s="8" t="s">
         <v>66</v>
       </c>
@@ -1381,7 +1372,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A36" s="8" t="s">
         <v>69</v>
       </c>
@@ -1390,7 +1381,7 @@
       </c>
       <c r="C36" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A37" s="8" t="s">
         <v>71</v>
       </c>
@@ -1401,7 +1392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A38" s="8" t="s">
         <v>74</v>
       </c>
@@ -1410,7 +1401,7 @@
       </c>
       <c r="C38" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A39" s="8" t="s">
         <v>76</v>
       </c>
@@ -1419,7 +1410,7 @@
       </c>
       <c r="C39" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A40" s="8" t="s">
         <v>78</v>
       </c>
@@ -1428,7 +1419,7 @@
       </c>
       <c r="C40" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A41" s="8" t="s">
         <v>80</v>
       </c>
@@ -1437,7 +1428,7 @@
       </c>
       <c r="C41" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A42" s="8" t="s">
         <v>82</v>
       </c>
@@ -1448,7 +1439,7 @@
         <v>84</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A43" s="8" t="s">
         <v>85</v>
       </c>
@@ -1459,7 +1450,7 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A44" s="8" t="s">
         <v>88</v>
       </c>
@@ -1468,7 +1459,7 @@
       </c>
       <c r="C44" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A45" s="8" t="s">
         <v>90</v>
       </c>
@@ -1479,7 +1470,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A46" s="8" t="s">
         <v>93</v>
       </c>
@@ -1490,7 +1481,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A47" s="8" t="s">
         <v>96</v>
       </c>
@@ -1499,7 +1490,7 @@
       </c>
       <c r="C47" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A48" s="8" t="s">
         <v>98</v>
       </c>
@@ -1508,7 +1499,7 @@
       </c>
       <c r="C48" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A49" s="8" t="s">
         <v>100</v>
       </c>
@@ -1517,7 +1508,7 @@
       </c>
       <c r="C49" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A50" s="8" t="s">
         <v>102</v>
       </c>
@@ -1526,7 +1517,7 @@
       </c>
       <c r="C50" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A51" s="8" t="s">
         <v>104</v>
       </c>
@@ -1537,7 +1528,7 @@
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A52" s="8" t="s">
         <v>107</v>
       </c>
@@ -1546,7 +1537,7 @@
       </c>
       <c r="C52" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A53" s="8" t="s">
         <v>109</v>
       </c>
@@ -1557,7 +1548,7 @@
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="82.5" customFormat="1" s="1">
       <c r="A54" s="8" t="s">
         <v>112</v>
       </c>
@@ -1568,7 +1559,7 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="33.75" customFormat="1" s="1">
       <c r="A55" s="8" t="s">
         <v>115</v>
       </c>
@@ -1577,7 +1568,7 @@
       </c>
       <c r="C55" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A56" s="8" t="s">
         <v>117</v>
       </c>
@@ -1586,7 +1577,7 @@
       </c>
       <c r="C56" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A57" s="8" t="s">
         <v>119</v>
       </c>
@@ -1597,7 +1588,7 @@
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A58" s="8" t="s">
         <v>122</v>
       </c>
@@ -1608,7 +1599,7 @@
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A59" s="8" t="s">
         <v>125</v>
       </c>
@@ -1617,7 +1608,7 @@
       </c>
       <c r="C59" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A60" s="8" t="s">
         <v>127</v>
       </c>
@@ -1628,7 +1619,7 @@
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A61" s="8" t="s">
         <v>130</v>
       </c>
@@ -1639,7 +1630,7 @@
         <v>132</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A62" s="8" t="s">
         <v>133</v>
       </c>
@@ -1650,7 +1641,7 @@
         <v>135</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A63" s="8" t="s">
         <v>136</v>
       </c>
@@ -1661,7 +1652,7 @@
         <v>138</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A64" s="8" t="s">
         <v>139</v>
       </c>
@@ -1670,7 +1661,7 @@
       </c>
       <c r="C64" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A65" s="8" t="s">
         <v>141</v>
       </c>
@@ -1679,7 +1670,7 @@
       </c>
       <c r="C65" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A66" s="8" t="s">
         <v>143</v>
       </c>
@@ -1688,7 +1679,7 @@
       </c>
       <c r="C66" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A67" s="8" t="s">
         <v>145</v>
       </c>
@@ -1699,7 +1690,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="44.25" customFormat="1" s="1">
       <c r="A68" s="8" t="s">
         <v>148</v>
       </c>
@@ -1710,7 +1701,7 @@
         <v>150</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A69" s="8" t="s">
         <v>151</v>
       </c>
@@ -1721,7 +1712,7 @@
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="31.5" customFormat="1" s="1">
       <c r="A70" s="8" t="s">
         <v>154</v>
       </c>
@@ -1732,7 +1723,7 @@
         <v>156</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="82.5" customFormat="1" s="1">
       <c r="A71" s="8" t="s">
         <v>157</v>
       </c>
@@ -1741,7 +1732,7 @@
       </c>
       <c r="C71" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A72" s="8" t="s">
         <v>159</v>
       </c>
@@ -1752,7 +1743,7 @@
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A73" s="8" t="s">
         <v>162</v>
       </c>
@@ -1761,7 +1752,7 @@
       </c>
       <c r="C73" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="82.5" customFormat="1" s="1">
       <c r="A74" s="8" t="s">
         <v>164</v>
       </c>
@@ -1770,7 +1761,7 @@
       </c>
       <c r="C74" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A75" s="8" t="s">
         <v>166</v>
       </c>
@@ -1781,7 +1772,7 @@
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="108" customFormat="1" s="1">
       <c r="A76" s="8" t="s">
         <v>169</v>
       </c>
@@ -1792,16 +1783,16 @@
         <v>171</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A77" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="13" t="s">
         <v>173</v>
       </c>
       <c r="C77" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A78" s="8" t="s">
         <v>174</v>
       </c>
@@ -1812,7 +1803,7 @@
         <v>176</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="57" customFormat="1" s="1">
       <c r="A79" s="8" t="s">
         <v>177</v>
       </c>
@@ -1821,7 +1812,7 @@
       </c>
       <c r="C79" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="95.25" customFormat="1" s="1">
       <c r="A80" s="8" t="s">
         <v>179</v>
       </c>
@@ -1830,7 +1821,7 @@
       </c>
       <c r="C80" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="69.75" customFormat="1" s="1">
       <c r="A81" s="8" t="s">
         <v>181</v>
       </c>
@@ -1841,361 +1832,361 @@
         <v>183</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="57.75" customFormat="1" s="1">
       <c r="A82" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>185</v>
       </c>
       <c r="C82" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="15.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4"/>
